--- a/exports/CHOLAFIN_full_report.xlsx
+++ b/exports/CHOLAFIN_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q70"/>
+  <dimension ref="A1:U70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>3.77</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44624.55208333334</v>
+        <v>44627.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>657.8</v>
+        <v>604.3</v>
       </c>
       <c r="I2" t="n">
         <v>638.5223752838516</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K2" t="n">
-        <v>16.92</v>
+        <v>7.41</v>
       </c>
       <c r="L2" t="n">
         <v>1.99</v>
@@ -555,7 +578,7 @@
         <v>3.06</v>
       </c>
       <c r="N2" t="n">
-        <v>5.65</v>
+        <v>7.81</v>
       </c>
       <c r="O2" t="n">
         <v>-1.66</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>15</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44631.55208333334</v>
+        <v>44634.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>669.95</v>
+        <v>674.8</v>
       </c>
       <c r="I3" t="n">
         <v>671.0951953972663</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>-10.86</v>
+        <v>-11.67</v>
       </c>
       <c r="L3" t="n">
-        <v>11.82</v>
+        <v>12.25</v>
       </c>
       <c r="M3" t="n">
         <v>1.23</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.84</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44658.38541666666</v>
+        <v>44658.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>692.95</v>
+        <v>687.95</v>
       </c>
       <c r="I4" t="n">
         <v>688.1567422515557</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>24</v>
+        <v>24.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>2.69</v>
+        <v>1.95</v>
       </c>
       <c r="L4" t="n">
         <v>2.48</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>5.99</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44658.55208333334</v>
+        <v>44659.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>687.95</v>
+        <v>742.45</v>
       </c>
       <c r="I5" t="n">
         <v>729.1507623717616</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>-7.92</v>
       </c>
       <c r="L5" t="n">
-        <v>0.87</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="O5" t="n">
         <v>-2.14</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44686.55208333334</v>
+        <v>44687.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>713.85</v>
+        <v>649.55</v>
       </c>
       <c r="I6" t="n">
         <v>706.2723022110571</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.85</v>
+        <v>-12.51</v>
       </c>
       <c r="L6" t="n">
-        <v>5.6</v>
+        <v>13.29</v>
       </c>
       <c r="M6" t="n">
-        <v>1.35</v>
+        <v>2.49</v>
       </c>
       <c r="N6" t="n">
-        <v>4.37</v>
+        <v>10.21</v>
       </c>
       <c r="O6" t="n">
         <v>8.029999999999999</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>14.44</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>655.05</v>
+        <v>676.95</v>
       </c>
       <c r="I7" t="n">
         <v>672.1530971255272</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.85</v>
+        <v>-4.22</v>
       </c>
       <c r="L7" t="n">
         <v>7.17</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>9.06</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>648.05</v>
+        <v>618.15</v>
       </c>
       <c r="I8" t="n">
         <v>636.0594291625342</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.27</v>
+        <v>-8.69</v>
       </c>
       <c r="L8" t="n">
-        <v>4.87</v>
+        <v>9.44</v>
       </c>
       <c r="M8" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="N8" t="n">
-        <v>4.03</v>
+        <v>5.56</v>
       </c>
       <c r="O8" t="n">
         <v>3.35</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>10.04</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44757.55208333334</v>
+        <v>44760.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>635.5</v>
+        <v>664.65</v>
       </c>
       <c r="I9" t="n">
         <v>653.6405739211589</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.81</v>
+        <v>-7.52</v>
       </c>
       <c r="L9" t="n">
-        <v>6.33</v>
+        <v>7.64</v>
       </c>
       <c r="M9" t="n">
         <v>1.8</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>5.27</v>
       </c>
       <c r="O9" t="n">
         <v>-5.56</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>780.1</v>
+        <v>739.6</v>
       </c>
       <c r="I10" t="n">
         <v>765.5771769825114</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>66.16666666666667</v>
+        <v>67</v>
       </c>
       <c r="K10" t="n">
-        <v>17.37</v>
+        <v>11.28</v>
       </c>
       <c r="L10" t="n">
         <v>4.3</v>
@@ -1011,7 +1130,7 @@
         <v>3.31</v>
       </c>
       <c r="N10" t="n">
-        <v>2.54</v>
+        <v>5.22</v>
       </c>
       <c r="O10" t="n">
         <v>5.27</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>10.06</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44866.55208333334</v>
+        <v>44867.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>708.05</v>
+        <v>751.75</v>
       </c>
       <c r="I11" t="n">
         <v>744.0249605548718</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K11" t="n">
-        <v>4.27</v>
+        <v>-1.64</v>
       </c>
       <c r="L11" t="n">
         <v>5.73</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44874.55208333334</v>
+        <v>44875.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>743.6</v>
+        <v>721.2</v>
       </c>
       <c r="I12" t="n">
         <v>723.7286792627584</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.08</v>
+        <v>-4.06</v>
       </c>
       <c r="L12" t="n">
         <v>5.82</v>
       </c>
       <c r="M12" t="n">
-        <v>0.37</v>
+        <v>0.48</v>
       </c>
       <c r="N12" t="n">
-        <v>2.01</v>
+        <v>2.9</v>
       </c>
       <c r="O12" t="n">
         <v>4.93</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>7.29</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44897.55208333334</v>
+        <v>44900.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>730.35</v>
+        <v>740.5</v>
       </c>
       <c r="I13" t="n">
         <v>735.5674207806653</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.27</v>
+        <v>-2.68</v>
       </c>
       <c r="L13" t="n">
         <v>3.81</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>4.45</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>735.9</v>
+        <v>723</v>
       </c>
       <c r="I14" t="n">
         <v>727.6002136850101</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.62</v>
+        <v>-2.36</v>
       </c>
       <c r="L14" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="M14" t="n">
         <v>0.38</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.08</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44939.38541666666</v>
+        <v>44939.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>706.95</v>
+        <v>711</v>
       </c>
       <c r="I15" t="n">
         <v>708.4442906528392</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>22.83333333333333</v>
+        <v>23</v>
       </c>
       <c r="K15" t="n">
-        <v>2.22</v>
+        <v>1.66</v>
       </c>
       <c r="L15" t="n">
         <v>2.04</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>6.14</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44979.55208333334</v>
+        <v>44980.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>764.5</v>
+        <v>752.45</v>
       </c>
       <c r="I16" t="n">
         <v>754.8292939465041</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>40</v>
+        <v>40.83333333333334</v>
       </c>
       <c r="K16" t="n">
-        <v>7.52</v>
+        <v>5.83</v>
       </c>
       <c r="L16" t="n">
         <v>5.02</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.27</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45014.55208333334</v>
+        <v>45016.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>750.1</v>
+        <v>761.35</v>
       </c>
       <c r="I17" t="n">
         <v>753.0895886676502</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K17" t="n">
-        <v>0.31</v>
+        <v>-1.18</v>
       </c>
       <c r="L17" t="n">
         <v>3.12</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>5.6</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45099.55208333334</v>
+        <v>45100.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>1100</v>
+        <v>1088.1</v>
       </c>
       <c r="I18" t="n">
         <v>1093.0381381766</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>83.16666666666667</v>
+        <v>84</v>
       </c>
       <c r="K18" t="n">
-        <v>44.48</v>
+        <v>42.92</v>
       </c>
       <c r="L18" t="n">
         <v>1.69</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>5.38</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45105.55208333334</v>
+        <v>45107.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>1125.35</v>
+        <v>1135.75</v>
       </c>
       <c r="I19" t="n">
         <v>1127.022265959056</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.42</v>
+        <v>-4.38</v>
       </c>
       <c r="L19" t="n">
-        <v>3.96</v>
+        <v>4.77</v>
       </c>
       <c r="M19" t="n">
         <v>0.92</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.3</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45131.55208333334</v>
+        <v>45132.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>1145.5</v>
+        <v>1122.1</v>
       </c>
       <c r="I20" t="n">
         <v>1128.003861915055</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K20" t="n">
-        <v>0.86</v>
+        <v>-1.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.44</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>7.42</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45160.38541666666</v>
+        <v>45160.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>1050.85</v>
+        <v>1063</v>
       </c>
       <c r="I21" t="n">
         <v>1060.479137119151</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>6.35</v>
+        <v>5.27</v>
       </c>
       <c r="L21" t="n">
         <v>3.01</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.33</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45217.55208333334</v>
+        <v>45218.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>1216.95</v>
+        <v>1200.9</v>
       </c>
       <c r="I22" t="n">
         <v>1203.119844839945</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>57</v>
+        <v>57.83333333333334</v>
       </c>
       <c r="K22" t="n">
-        <v>14.48</v>
+        <v>12.97</v>
       </c>
       <c r="L22" t="n">
         <v>1.22</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>4.98</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45264.38541666666</v>
+        <v>45264.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>1145.7</v>
+        <v>1150</v>
       </c>
       <c r="I23" t="n">
         <v>1148.528431879242</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>46</v>
+        <v>46.16666666666666</v>
       </c>
       <c r="K23" t="n">
-        <v>4.6</v>
+        <v>4.24</v>
       </c>
       <c r="L23" t="n">
         <v>1.38</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>4.8</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45300.55208333334</v>
+        <v>45301.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>1233</v>
+        <v>1211.75</v>
       </c>
       <c r="I24" t="n">
         <v>1224.361902171119</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K24" t="n">
-        <v>7.22</v>
+        <v>5.37</v>
       </c>
       <c r="L24" t="n">
         <v>1.89</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>6.62</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45303.55208333334</v>
+        <v>45306.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>1252</v>
+        <v>1281.2</v>
       </c>
       <c r="I25" t="n">
         <v>1280.540214736856</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.32</v>
+        <v>-5.73</v>
       </c>
       <c r="L25" t="n">
-        <v>3.32</v>
+        <v>6.43</v>
       </c>
       <c r="M25" t="n">
         <v>0.57</v>
       </c>
       <c r="N25" t="n">
-        <v>1.71</v>
+        <v>2.18</v>
       </c>
       <c r="O25" t="n">
         <v>-1.3</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>5.86</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>1258</v>
+        <v>1228.5</v>
       </c>
       <c r="I26" t="n">
         <v>1239.334053603925</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.81</v>
+        <v>-4.11</v>
       </c>
       <c r="L26" t="n">
-        <v>3.04</v>
+        <v>4.55</v>
       </c>
       <c r="M26" t="n">
         <v>1.06</v>
       </c>
       <c r="N26" t="n">
-        <v>1.63</v>
+        <v>3.49</v>
       </c>
       <c r="O26" t="n">
         <v>2.18</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>9.49</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45358.55208333334</v>
+        <v>45362.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>1082</v>
+        <v>1099.2</v>
       </c>
       <c r="I27" t="n">
         <v>1086.822711441685</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K27" t="n">
-        <v>11.93</v>
+        <v>10.53</v>
       </c>
       <c r="L27" t="n">
         <v>5.52</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>7.2</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45397.55208333334</v>
+        <v>45398.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>1167.95</v>
+        <v>1130.6</v>
       </c>
       <c r="I28" t="n">
         <v>1155.360491818084</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K28" t="n">
-        <v>6.25</v>
+        <v>2.86</v>
       </c>
       <c r="L28" t="n">
         <v>6.6</v>
@@ -2037,7 +2372,7 @@
         <v>2.62</v>
       </c>
       <c r="N28" t="n">
-        <v>2.28</v>
+        <v>3.12</v>
       </c>
       <c r="O28" t="n">
         <v>0.87</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>7.04</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45408.38541666666</v>
+        <v>45408.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>1155.9</v>
+        <v>1172</v>
       </c>
       <c r="I29" t="n">
         <v>1171.474939525979</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.24</v>
+        <v>-3.66</v>
       </c>
       <c r="L29" t="n">
-        <v>4.48</v>
+        <v>4.79</v>
       </c>
       <c r="M29" t="n">
         <v>0.92</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.8</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45420.55208333334</v>
+        <v>45421.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>1266</v>
+        <v>1228</v>
       </c>
       <c r="I30" t="n">
         <v>1241.735097026828</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>8.02</v>
+        <v>4.78</v>
       </c>
       <c r="L30" t="n">
         <v>1.84</v>
@@ -2151,7 +2510,7 @@
         <v>0.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.91</v>
+        <v>3.32</v>
       </c>
       <c r="O30" t="n">
         <v>1.53</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>9.26</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>1245.5</v>
+        <v>1281.7</v>
       </c>
       <c r="I31" t="n">
         <v>1280.855160914301</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.43</v>
+        <v>-4.37</v>
       </c>
       <c r="L31" t="n">
         <v>6.57</v>
       </c>
       <c r="M31" t="n">
-        <v>0.89</v>
+        <v>1.97</v>
       </c>
       <c r="N31" t="n">
         <v>4.12</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>6.4</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>1408.4</v>
+        <v>1374.2</v>
       </c>
       <c r="I32" t="n">
         <v>1375.798360869709</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K32" t="n">
-        <v>9.890000000000001</v>
+        <v>7.22</v>
       </c>
       <c r="L32" t="n">
         <v>6.56</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>7.86</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45499.55208333334</v>
+        <v>45502.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>1415</v>
+        <v>1472.15</v>
       </c>
       <c r="I33" t="n">
         <v>1451.598823806888</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.97</v>
+        <v>-7.13</v>
       </c>
       <c r="L33" t="n">
-        <v>4.58</v>
+        <v>7.48</v>
       </c>
       <c r="M33" t="n">
         <v>0.4</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>11.93</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45516.55208333334</v>
+        <v>45517.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>1352</v>
+        <v>1321.25</v>
       </c>
       <c r="I34" t="n">
         <v>1321.823204200301</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K34" t="n">
-        <v>-8.16</v>
+        <v>-10.25</v>
       </c>
       <c r="L34" t="n">
-        <v>9.720000000000001</v>
+        <v>10.42</v>
       </c>
       <c r="M34" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>2.58</v>
+        <v>2.96</v>
       </c>
       <c r="O34" t="n">
         <v>1.27</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>8.26</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45525.38541666666</v>
+        <v>45525.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>1386.8</v>
+        <v>1402</v>
       </c>
       <c r="I35" t="n">
         <v>1399.171728064454</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>-4.96</v>
+        <v>-6.11</v>
       </c>
       <c r="L35" t="n">
-        <v>5.96</v>
+        <v>6.29</v>
       </c>
       <c r="M35" t="n">
         <v>0.5600000000000001</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>5.55</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45566.55208333334</v>
+        <v>45568.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>1585</v>
+        <v>1516.8</v>
       </c>
       <c r="I36" t="n">
         <v>1559.926653394291</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>41</v>
+        <v>42.83333333333334</v>
       </c>
       <c r="K36" t="n">
-        <v>13.05</v>
+        <v>8.19</v>
       </c>
       <c r="L36" t="n">
         <v>4.12</v>
@@ -2493,7 +2924,7 @@
         <v>1.83</v>
       </c>
       <c r="N36" t="n">
-        <v>3.07</v>
+        <v>4.04</v>
       </c>
       <c r="O36" t="n">
         <v>1.15</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>7.84</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45573.55208333334</v>
+        <v>45574.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>1533</v>
+        <v>1570</v>
       </c>
       <c r="I37" t="n">
         <v>1557.675009777392</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.07</v>
+        <v>-3.51</v>
       </c>
       <c r="L37" t="n">
-        <v>3.86</v>
+        <v>4.62</v>
       </c>
       <c r="M37" t="n">
         <v>0.66</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>6.72</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45581.55208333334</v>
+        <v>45582.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>1480.4</v>
+        <v>1451.95</v>
       </c>
       <c r="I38" t="n">
         <v>1465.337811085053</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K38" t="n">
-        <v>-5.71</v>
+        <v>-7.52</v>
       </c>
       <c r="L38" t="n">
-        <v>6.09</v>
+        <v>7.58</v>
       </c>
       <c r="M38" t="n">
         <v>0.09</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>7.7</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45622.55208333334</v>
+        <v>45623.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>1263.3</v>
+        <v>1288.95</v>
       </c>
       <c r="I39" t="n">
         <v>1280.388324089752</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K39" t="n">
-        <v>12.99</v>
+        <v>11.23</v>
       </c>
       <c r="L39" t="n">
         <v>3</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>7.48</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45642.55208333334</v>
+        <v>45643.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>1285.05</v>
+        <v>1256.1</v>
       </c>
       <c r="I40" t="n">
         <v>1282.193108082487</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.3</v>
+        <v>-2.55</v>
       </c>
       <c r="L40" t="n">
         <v>4.65</v>
@@ -2721,7 +3200,7 @@
         <v>0.77</v>
       </c>
       <c r="N40" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="O40" t="n">
         <v>1.31</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.03</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>1186.95</v>
+        <v>1254.8</v>
       </c>
       <c r="I41" t="n">
         <v>1242.604707565944</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K41" t="n">
-        <v>5.51</v>
+        <v>0.1</v>
       </c>
       <c r="L41" t="n">
         <v>2.53</v>
@@ -2778,7 +3269,7 @@
         <v>1.53</v>
       </c>
       <c r="N41" t="n">
-        <v>1.53</v>
+        <v>6.99</v>
       </c>
       <c r="O41" t="n">
         <v>-3.1</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>8.75</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45667.55208333334</v>
+        <v>45670.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>1251</v>
+        <v>1225.3</v>
       </c>
       <c r="I42" t="n">
         <v>1240.040678865984</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.3</v>
+        <v>-2.35</v>
       </c>
       <c r="L42" t="n">
         <v>5.72</v>
       </c>
       <c r="M42" t="n">
-        <v>0.32</v>
+        <v>1.68</v>
       </c>
       <c r="N42" t="n">
         <v>2.72</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>7.84</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45685.55208333334</v>
+        <v>45686.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>1234</v>
+        <v>1292.4</v>
       </c>
       <c r="I43" t="n">
         <v>1263.172423134402</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.71</v>
+        <v>-5.48</v>
       </c>
       <c r="L43" t="n">
-        <v>5.93</v>
+        <v>6.01</v>
       </c>
       <c r="M43" t="n">
         <v>2.5</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,25 +3455,25 @@
         <v>11.11</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>1469</v>
+        <v>1439.85</v>
       </c>
       <c r="I44" t="n">
         <v>1466.153321301549</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>62.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K44" t="n">
-        <v>13.66</v>
+        <v>11.41</v>
       </c>
       <c r="L44" t="n">
         <v>5.19</v>
       </c>
       <c r="M44" t="n">
-        <v>0.72</v>
+        <v>1.02</v>
       </c>
       <c r="N44" t="n">
         <v>3.7</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>4</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>7.69</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>1468.9</v>
+        <v>1538.5</v>
       </c>
       <c r="I45" t="n">
         <v>1483.306465312452</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.02</v>
+        <v>-6.85</v>
       </c>
       <c r="L45" t="n">
-        <v>4.08</v>
+        <v>7.16</v>
       </c>
       <c r="M45" t="n">
-        <v>2.72</v>
+        <v>3.48</v>
       </c>
       <c r="N45" t="n">
-        <v>5.84</v>
+        <v>6.2</v>
       </c>
       <c r="O45" t="n">
         <v>-1.5</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.869999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45772.38541666666</v>
+        <v>45772.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>1543.4</v>
+        <v>1529</v>
       </c>
       <c r="I46" t="n">
         <v>1532.50555969927</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K46" t="n">
-        <v>0.32</v>
+        <v>-0.62</v>
       </c>
       <c r="L46" t="n">
         <v>3.29</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>9.6</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45791.55208333334</v>
+        <v>45792.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>1599</v>
+        <v>1611.9</v>
       </c>
       <c r="I47" t="n">
         <v>1599.516006462237</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>-4.58</v>
+        <v>-5.42</v>
       </c>
       <c r="L47" t="n">
-        <v>5.04</v>
+        <v>5.43</v>
       </c>
       <c r="M47" t="n">
         <v>1.95</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,25 +3731,25 @@
         <v>7.19</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45807.55208333334</v>
+        <v>45810.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>1597.9</v>
+        <v>1558.1</v>
       </c>
       <c r="I48" t="n">
         <v>1591.554283417239</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.87</v>
+        <v>-3.34</v>
       </c>
       <c r="L48" t="n">
-        <v>2.3</v>
+        <v>3.96</v>
       </c>
       <c r="M48" t="n">
-        <v>0.9</v>
+        <v>1.75</v>
       </c>
       <c r="N48" t="n">
         <v>1.98</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>5.83</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45813.55208333334</v>
+        <v>45814.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>1515.2</v>
+        <v>1607.8</v>
       </c>
       <c r="I49" t="n">
         <v>1593.739880590813</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K49" t="n">
-        <v>2.75</v>
+        <v>-3.19</v>
       </c>
       <c r="L49" t="n">
-        <v>2.89</v>
+        <v>4.21</v>
       </c>
       <c r="M49" t="n">
         <v>0.53</v>
       </c>
       <c r="N49" t="n">
-        <v>0.08</v>
+        <v>5</v>
       </c>
       <c r="O49" t="n">
         <v>-0.71</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>9.880000000000001</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45839.55208333334</v>
+        <v>45840.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>1600</v>
+        <v>1548</v>
       </c>
       <c r="I50" t="n">
         <v>1573.14347466651</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.49</v>
+        <v>-3.72</v>
       </c>
       <c r="L50" t="n">
         <v>6.88</v>
@@ -3291,7 +3890,7 @@
         <v>1.83</v>
       </c>
       <c r="N50" t="n">
-        <v>2.52</v>
+        <v>2.83</v>
       </c>
       <c r="O50" t="n">
         <v>5</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>7.94</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>1459</v>
+        <v>1525.5</v>
       </c>
       <c r="I51" t="n">
         <v>1517.386620821238</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K51" t="n">
-        <v>5.75</v>
+        <v>1.45</v>
       </c>
       <c r="L51" t="n">
         <v>3.71</v>
       </c>
       <c r="M51" t="n">
-        <v>1.09</v>
+        <v>2.81</v>
       </c>
       <c r="N51" t="n">
-        <v>3.56</v>
+        <v>4.18</v>
       </c>
       <c r="O51" t="n">
         <v>-2.83</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>6.52</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45895.55208333334</v>
+        <v>45897.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>1477.4</v>
+        <v>1447.5</v>
       </c>
       <c r="I52" t="n">
         <v>1461.275349260817</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.15</v>
+        <v>-5.11</v>
       </c>
       <c r="L52" t="n">
-        <v>3.63</v>
+        <v>5.39</v>
       </c>
       <c r="M52" t="n">
-        <v>0.2</v>
+        <v>0.89</v>
       </c>
       <c r="N52" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="O52" t="n">
         <v>4.18</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>5.19</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45905.55208333334</v>
+        <v>45908.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>1491</v>
+        <v>1505</v>
       </c>
       <c r="I53" t="n">
         <v>1493.721057860921</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.01</v>
+        <v>-3.97</v>
       </c>
       <c r="L53" t="n">
-        <v>3.33</v>
+        <v>4.59</v>
       </c>
       <c r="M53" t="n">
         <v>2.15</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,25 +4145,25 @@
         <v>5.03</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45981.55208333334</v>
+        <v>45982.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>1708</v>
+        <v>1663.9</v>
       </c>
       <c r="I54" t="n">
         <v>1664.430003417323</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>73.16666666666667</v>
+        <v>74</v>
       </c>
       <c r="K54" t="n">
-        <v>13.49</v>
+        <v>10.56</v>
       </c>
       <c r="L54" t="n">
         <v>1.55</v>
       </c>
       <c r="M54" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="N54" t="n">
         <v>4.01</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>5.81</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45988.55208333334</v>
+        <v>45989.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>1730.5</v>
+        <v>1740</v>
       </c>
       <c r="I55" t="n">
         <v>1734.81365352768</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K55" t="n">
-        <v>-4</v>
+        <v>-4.57</v>
       </c>
       <c r="L55" t="n">
         <v>5.16</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>5.06</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46009.55208333334</v>
+        <v>46010.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>1683</v>
+        <v>1621.7</v>
       </c>
       <c r="I56" t="n">
         <v>1666.545334348409</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K56" t="n">
-        <v>-3.28</v>
+        <v>-6.8</v>
       </c>
       <c r="L56" t="n">
-        <v>5.11</v>
+        <v>7.13</v>
       </c>
       <c r="M56" t="n">
         <v>0.93</v>
       </c>
       <c r="N56" t="n">
-        <v>2.44</v>
+        <v>2.63</v>
       </c>
       <c r="O56" t="n">
         <v>0.32</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>7.61</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46022.55208333334</v>
+        <v>46023.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>1702</v>
+        <v>1713.4</v>
       </c>
       <c r="I57" t="n">
         <v>1707.194812483064</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K57" t="n">
-        <v>-4.95</v>
+        <v>-5.65</v>
       </c>
       <c r="L57" t="n">
-        <v>5.81</v>
+        <v>6.25</v>
       </c>
       <c r="M57" t="n">
         <v>1.26</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>5.13</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46031.55208333334</v>
+        <v>46034.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1722</v>
+        <v>1712.2</v>
       </c>
       <c r="I58" t="n">
         <v>1719.636374663841</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K58" t="n">
-        <v>0.5</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>0.86</v>
+        <v>1.17</v>
       </c>
       <c r="M58" t="n">
-        <v>0.06</v>
+        <v>0.41</v>
       </c>
       <c r="N58" t="n">
         <v>1.88</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>5.24</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>1594</v>
+        <v>1697.7</v>
       </c>
       <c r="I59" t="n">
         <v>1662.682393274646</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K59" t="n">
-        <v>6.9</v>
+        <v>0.85</v>
       </c>
       <c r="L59" t="n">
-        <v>1.09</v>
+        <v>1.62</v>
       </c>
       <c r="M59" t="n">
-        <v>0.51</v>
+        <v>6.01</v>
       </c>
       <c r="N59" t="n">
-        <v>1.97</v>
+        <v>6.42</v>
       </c>
       <c r="O59" t="n">
         <v>-0.82</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.69</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>1695.8</v>
+        <v>1640.1</v>
       </c>
       <c r="I60" t="n">
         <v>1666.10372151292</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.11</v>
+        <v>-3.39</v>
       </c>
       <c r="L60" t="n">
         <v>4.11</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>1402.1</v>
+        <v>1544.8</v>
       </c>
       <c r="I61" t="n">
         <v>1452.923243767106</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K61" t="n">
-        <v>14.51</v>
+        <v>5.81</v>
       </c>
       <c r="L61" t="n">
         <v>3.4</v>
       </c>
       <c r="M61" t="n">
-        <v>3.78</v>
+        <v>7.2</v>
       </c>
       <c r="N61" t="n">
-        <v>3.23</v>
+        <v>10.91</v>
       </c>
       <c r="O61" t="n">
         <v>-2.57</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>10.36</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46154.38541666666</v>
+        <v>46154.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>1589</v>
+        <v>1578.3</v>
       </c>
       <c r="I62" t="n">
         <v>1580.433739775316</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>34</v>
+        <v>34.16666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>2.86</v>
+        <v>2.17</v>
       </c>
       <c r="L62" t="n">
         <v>4.69</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.66</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46167.38541666666</v>
+        <v>46167.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>1586.6</v>
+        <v>1592</v>
       </c>
       <c r="I63" t="n">
         <v>1591.346741736067</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>12.83333333333333</v>
+        <v>13</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.53</v>
+        <v>-0.87</v>
       </c>
       <c r="L63" t="n">
         <v>1.37</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,22 +4835,22 @@
         <v>5.99</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46174.38541666666</v>
+        <v>46174.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>1503.5</v>
+        <v>1492.3</v>
       </c>
       <c r="I64" t="n">
         <v>1497.71138247227</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K64" t="n">
-        <v>-5.56</v>
+        <v>-6.26</v>
       </c>
       <c r="L64" t="n">
-        <v>5.59</v>
+        <v>6.6</v>
       </c>
       <c r="M64" t="n">
         <v>0.98</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>6.53</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46185.38541666666</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>1492.9</v>
+        <v>1566.3</v>
       </c>
       <c r="I65" t="n">
         <v>1545.64235668883</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>10.83333333333333</v>
+        <v>11</v>
       </c>
       <c r="K65" t="n">
-        <v>-0.04</v>
+        <v>-4.96</v>
       </c>
       <c r="L65" t="n">
-        <v>3.8</v>
+        <v>5.72</v>
       </c>
       <c r="M65" t="n">
         <v>1.67</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>9.34</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>1848</v>
+        <v>1767</v>
       </c>
       <c r="I66" t="n">
         <v>1768.206415277095</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>25.83333333333333</v>
+        <v>26</v>
       </c>
       <c r="K66" t="n">
-        <v>17.99</v>
+        <v>12.81</v>
       </c>
       <c r="L66" t="n">
         <v>4.86</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46227.55208333334</v>
+        <v>46230.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>1721.5</v>
+        <v>1796</v>
       </c>
       <c r="I67" t="n">
         <v>1784.527041282178</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>2.57</v>
+        <v>-1.64</v>
       </c>
       <c r="L67" t="n">
         <v>4.65</v>
       </c>
       <c r="M67" t="n">
-        <v>0.4</v>
+        <v>1.31</v>
       </c>
       <c r="N67" t="n">
-        <v>2.04</v>
+        <v>3.6</v>
       </c>
       <c r="O67" t="n">
         <v>-4.5</v>
@@ -4269,7 +5072,19 @@
         <v>1</v>
       </c>
       <c r="Q67" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>7</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46266.38541666666</v>
+        <v>46266.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>1836</v>
+        <v>1811.9</v>
       </c>
       <c r="I68" t="n">
         <v>1829.243572851849</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K68" t="n">
-        <v>2.23</v>
+        <v>0.89</v>
       </c>
       <c r="L68" t="n">
         <v>5.56</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>3</v>
+      </c>
+      <c r="U68" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>4.92</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46323.38541666666</v>
+        <v>46323.55208333334</v>
       </c>
       <c r="H69" t="n">
-        <v>1497.4</v>
+        <v>1554</v>
       </c>
       <c r="I69" t="n">
         <v>1541.190527816223</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>56.83333333333334</v>
+        <v>57</v>
       </c>
       <c r="K69" t="n">
-        <v>17.36</v>
+        <v>14.23</v>
       </c>
       <c r="L69" t="n">
         <v>3.11</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>3</v>
+      </c>
+      <c r="U69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -4434,6 +5273,12 @@
       <c r="Q70" t="n">
         <v>1</v>
       </c>
+      <c r="R70" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6536,7 +7381,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.4</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="6">
@@ -6546,7 +7391,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.7</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="7">
@@ -6556,7 +7401,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>83.2</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -6566,7 +7411,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="9">
@@ -6576,7 +7421,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -6586,7 +7431,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50.4</v>
+        <v>51.8</v>
       </c>
     </row>
     <row r="11">
@@ -6626,7 +7471,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.99</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -6636,7 +7481,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4.71</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="16">
@@ -6646,7 +7491,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.26</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="17">
@@ -6656,7 +7501,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>44.48</v>
+        <v>42.92</v>
       </c>
     </row>
     <row r="18">
@@ -6666,7 +7511,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.5</v>
+        <v>38.2</v>
       </c>
     </row>
     <row r="19">
@@ -6676,7 +7521,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.17</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="20">
@@ -6686,7 +7531,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.1</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="21">
@@ -6696,7 +7541,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>11.82</v>
+        <v>13.29</v>
       </c>
     </row>
     <row r="22">
@@ -6706,7 +7551,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23">
@@ -6716,7 +7561,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -6726,7 +7571,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.32</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="25">
@@ -6736,7 +7581,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.02</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="26">
@@ -6746,7 +7591,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.3</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="27">
@@ -6756,7 +7601,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6.91</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="28">
@@ -6766,7 +7611,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
